--- a/events/Pau_2017_WWC/Pau_2017_WWC_start.xlsx
+++ b/events/Pau_2017_WWC/Pau_2017_WWC_start.xlsx
@@ -610,11 +610,6 @@
       <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>FR C1M</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -663,11 +658,6 @@
       <c r="K3" t="n">
         <v>2</v>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>FR K1W</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -716,11 +706,6 @@
       <c r="K4" t="n">
         <v>3</v>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>FR K1M 1</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -768,11 +753,6 @@
       </c>
       <c r="K5" t="n">
         <v>4</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>FR K1M 2</t>
-        </is>
       </c>
     </row>
     <row r="6">

--- a/events/Pau_2017_WWC/Pau_2017_WWC_start.xlsx
+++ b/events/Pau_2017_WWC/Pau_2017_WWC_start.xlsx
@@ -599,11 +599,6 @@
           <t>14:00:00</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>TIP</t>
-        </is>
-      </c>
       <c r="J2" t="n">
         <v>138</v>
       </c>
@@ -647,11 +642,6 @@
           <t>14:02:00</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>TIP</t>
-        </is>
-      </c>
       <c r="J3" t="n">
         <v>137</v>
       </c>
@@ -695,11 +685,6 @@
           <t>14:04:00</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>TIP</t>
-        </is>
-      </c>
       <c r="J4" t="n">
         <v>136</v>
       </c>
@@ -741,11 +726,6 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>14:06:00</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>TIP</t>
         </is>
       </c>
       <c r="J5" t="n">
